--- a/rgb_workover_operations/report/excel_templates/daily_report_template.xlsx
+++ b/rgb_workover_operations/report/excel_templates/daily_report_template.xlsx
@@ -204,7 +204,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="94">
+  <borders count="106">
     <border>
       <left/>
       <right/>
@@ -1422,12 +1422,148 @@
       <top/>
       <bottom/>
       <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="double">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="double">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="double">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="double">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="double">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="190">
+  <cellXfs count="200">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1933,6 +2069,26 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="84" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="97" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="95" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="98" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="2" borderId="99" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="101" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="99" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="102" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="100" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="99" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2315,7 +2471,7 @@
     <col width="8.14062" customWidth="1" min="11" max="11"/>
     <col width="1.57031" customWidth="1" min="12" max="12"/>
     <col width="10.1406" customWidth="1" min="13" max="13"/>
-    <col width="9.14062" customWidth="1" min="14" max="14"/>
+    <col width="0.1" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.1" customHeight="1">
@@ -2934,26 +3090,21 @@
           <t>TO</t>
         </is>
       </c>
-      <c r="C22" s="96" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="D22" s="97" t="n"/>
+      <c r="C22" s="192" t="n"/>
+      <c r="D22" s="37" t="n"/>
       <c r="E22" s="37" t="n"/>
       <c r="F22" s="37" t="n"/>
       <c r="G22" s="37" t="n"/>
       <c r="H22" s="37" t="n"/>
       <c r="I22" s="37" t="n"/>
-      <c r="J22" s="40" t="n"/>
-      <c r="K22" s="98" t="inlineStr">
+      <c r="J22" s="41" t="inlineStr">
         <is>
           <t>TIME BREAK DOWN</t>
         </is>
       </c>
+      <c r="K22" s="37" t="n"/>
       <c r="L22" s="37" t="n"/>
-      <c r="M22" s="37" t="n"/>
-      <c r="N22" s="40" t="n"/>
+      <c r="M22" s="40" t="n"/>
       <c r="P22" s="99" t="n"/>
     </row>
     <row r="23" ht="12" customHeight="1">
@@ -2963,28 +3114,27 @@
       <c r="B23" s="101" t="n">
         <v>0.75</v>
       </c>
-      <c r="C23" s="102" t="inlineStr">
+      <c r="C23" s="193" t="inlineStr">
         <is>
           <t>RIG MOVE &amp; RIG /UP</t>
         </is>
       </c>
-      <c r="D23" s="103" t="inlineStr">
-        <is>
-          <t>MOVE RIG &amp; RIG EQUIP F/G-71-91 TO D-43-H DISTANCE ONE WAY 15 KM 100%</t>
-        </is>
-      </c>
+      <c r="D23" s="104" t="n"/>
       <c r="E23" s="104" t="n"/>
       <c r="F23" s="104" t="n"/>
       <c r="G23" s="104" t="n"/>
       <c r="H23" s="104" t="n"/>
       <c r="I23" s="104" t="n"/>
-      <c r="J23" s="105" t="n"/>
-      <c r="K23" s="106" t="inlineStr">
+      <c r="J23" s="51" t="inlineStr">
         <is>
           <t>OPERATION</t>
         </is>
       </c>
-      <c r="L23" s="104" t="n"/>
+      <c r="K23" s="44" t="n"/>
+      <c r="L23" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="53" t="n"/>
       <c r="N23" s="107" t="n">
         <v>0</v>
       </c>
@@ -2992,24 +3142,22 @@
     <row r="24" ht="9.75" customHeight="1">
       <c r="A24" s="100" t="n"/>
       <c r="B24" s="101" t="n"/>
-      <c r="C24" s="108" t="n"/>
-      <c r="D24" s="103" t="inlineStr">
-        <is>
-          <t>CLEAN LEVEL LOCATION</t>
-        </is>
-      </c>
+      <c r="C24" s="195" t="n"/>
+      <c r="D24" s="104" t="n"/>
       <c r="E24" s="104" t="n"/>
       <c r="F24" s="104" t="n"/>
       <c r="G24" s="104" t="n"/>
       <c r="H24" s="104" t="n"/>
       <c r="I24" s="104" t="n"/>
-      <c r="J24" s="105" t="n"/>
-      <c r="K24" s="109" t="inlineStr">
+      <c r="J24" s="51" t="inlineStr">
         <is>
           <t>RIG MOVE &amp; RIG /UP</t>
         </is>
       </c>
-      <c r="L24" s="49" t="n"/>
+      <c r="K24" s="44" t="n"/>
+      <c r="L24" s="52" t="n">
+        <v>5</v>
+      </c>
       <c r="M24" s="53" t="n"/>
       <c r="N24" s="107" t="n">
         <v>5</v>
@@ -3020,25 +3168,23 @@
     <row r="25" ht="9.75" customHeight="1">
       <c r="A25" s="100" t="n"/>
       <c r="B25" s="101" t="n"/>
-      <c r="C25" s="108" t="n"/>
-      <c r="D25" s="103" t="inlineStr">
-        <is>
-          <t>DISCONNECT PRODCTION LINE</t>
-        </is>
-      </c>
+      <c r="C25" s="195" t="n"/>
+      <c r="D25" s="104" t="n"/>
       <c r="E25" s="104" t="n"/>
       <c r="F25" s="104" t="n"/>
       <c r="G25" s="104" t="n"/>
       <c r="H25" s="104" t="n"/>
       <c r="I25" s="104" t="n"/>
-      <c r="J25" s="105" t="n"/>
-      <c r="K25" s="112" t="inlineStr">
+      <c r="J25" s="51" t="inlineStr">
         <is>
           <t>STANDBY W/CREW</t>
         </is>
       </c>
-      <c r="L25" s="22" t="n"/>
-      <c r="M25" s="27" t="n"/>
+      <c r="K25" s="44" t="n"/>
+      <c r="L25" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="53" t="n"/>
       <c r="N25" s="107" t="n">
         <v>0</v>
       </c>
@@ -3046,25 +3192,23 @@
     <row r="26" ht="10.5" customHeight="1">
       <c r="A26" s="100" t="n"/>
       <c r="B26" s="101" t="n"/>
-      <c r="C26" s="108" t="n"/>
-      <c r="D26" s="103" t="inlineStr">
-        <is>
-          <t>SPOT RIG &amp; RIG EQUIP INSIDE LOC 40%</t>
-        </is>
-      </c>
+      <c r="C26" s="195" t="n"/>
+      <c r="D26" s="104" t="n"/>
       <c r="E26" s="104" t="n"/>
       <c r="F26" s="104" t="n"/>
       <c r="G26" s="104" t="n"/>
       <c r="H26" s="104" t="n"/>
       <c r="I26" s="104" t="n"/>
-      <c r="J26" s="105" t="n"/>
-      <c r="K26" s="112" t="inlineStr">
+      <c r="J26" s="51" t="inlineStr">
         <is>
           <t>DOWN TIME</t>
         </is>
       </c>
-      <c r="L26" s="22" t="n"/>
-      <c r="M26" s="27" t="n"/>
+      <c r="K26" s="44" t="n"/>
+      <c r="L26" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="53" t="n"/>
       <c r="N26" s="107" t="n">
         <v>0</v>
       </c>
@@ -3072,21 +3216,23 @@
     <row r="27" ht="9.75" customHeight="1">
       <c r="A27" s="100" t="n"/>
       <c r="B27" s="101" t="n"/>
-      <c r="C27" s="108" t="n"/>
-      <c r="D27" s="103" t="n"/>
+      <c r="C27" s="195" t="n"/>
+      <c r="D27" s="104" t="n"/>
       <c r="E27" s="104" t="n"/>
       <c r="F27" s="104" t="n"/>
       <c r="G27" s="104" t="n"/>
       <c r="H27" s="104" t="n"/>
       <c r="I27" s="104" t="n"/>
-      <c r="J27" s="105" t="n"/>
-      <c r="K27" s="112" t="inlineStr">
+      <c r="J27" s="51" t="inlineStr">
         <is>
           <t xml:space="preserve">SHUT DOWN </t>
         </is>
       </c>
-      <c r="L27" s="22" t="n"/>
-      <c r="M27" s="27" t="n"/>
+      <c r="K27" s="44" t="n"/>
+      <c r="L27" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="53" t="n"/>
       <c r="N27" s="107" t="n">
         <v>0</v>
       </c>
@@ -3095,21 +3241,23 @@
     <row r="28" ht="9.75" customHeight="1">
       <c r="A28" s="100" t="n"/>
       <c r="B28" s="101" t="n"/>
-      <c r="C28" s="108" t="n"/>
-      <c r="D28" s="103" t="n"/>
+      <c r="C28" s="195" t="n"/>
+      <c r="D28" s="104" t="n"/>
       <c r="E28" s="104" t="n"/>
       <c r="F28" s="104" t="n"/>
       <c r="G28" s="104" t="n"/>
       <c r="H28" s="104" t="n"/>
       <c r="I28" s="104" t="n"/>
-      <c r="J28" s="105" t="n"/>
-      <c r="K28" s="112" t="inlineStr">
+      <c r="J28" s="51" t="inlineStr">
         <is>
           <t>REPAIR</t>
         </is>
       </c>
-      <c r="L28" s="22" t="n"/>
-      <c r="M28" s="27" t="n"/>
+      <c r="K28" s="44" t="n"/>
+      <c r="L28" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="53" t="n"/>
       <c r="N28" s="107" t="n">
         <v>0</v>
       </c>
@@ -3117,17 +3265,19 @@
     <row r="29" ht="10.5" customHeight="1">
       <c r="A29" s="100" t="n"/>
       <c r="B29" s="101" t="n"/>
-      <c r="C29" s="108" t="n"/>
-      <c r="D29" s="103" t="n"/>
+      <c r="C29" s="195" t="n"/>
+      <c r="D29" s="104" t="n"/>
       <c r="E29" s="104" t="n"/>
       <c r="F29" s="104" t="n"/>
       <c r="G29" s="104" t="n"/>
       <c r="H29" s="104" t="n"/>
       <c r="I29" s="104" t="n"/>
-      <c r="J29" s="105" t="n"/>
-      <c r="K29" s="114" t="n"/>
-      <c r="L29" s="22" t="n"/>
-      <c r="M29" s="27" t="n"/>
+      <c r="J29" s="51" t="n"/>
+      <c r="K29" s="44" t="n"/>
+      <c r="L29" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="53" t="n"/>
       <c r="N29" s="107" t="n">
         <v>0</v>
       </c>
@@ -3136,21 +3286,24 @@
     <row r="30" ht="12.95" customHeight="1">
       <c r="A30" s="100" t="n"/>
       <c r="B30" s="101" t="n"/>
-      <c r="C30" s="108" t="n"/>
-      <c r="D30" s="116" t="n"/>
+      <c r="C30" s="195" t="n"/>
+      <c r="D30" s="104" t="n"/>
       <c r="E30" s="104" t="n"/>
       <c r="F30" s="104" t="n"/>
       <c r="G30" s="104" t="n"/>
       <c r="H30" s="104" t="n"/>
       <c r="I30" s="104" t="n"/>
-      <c r="J30" s="105" t="n"/>
-      <c r="K30" s="117" t="n"/>
-      <c r="L30" s="118" t="inlineStr">
+      <c r="J30" s="51" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="M30" s="29" t="n"/>
+      <c r="K30" s="44" t="n"/>
+      <c r="L30" s="52">
+        <f>SUM(L23:L29)</f>
+        <v/>
+      </c>
+      <c r="M30" s="53" t="n"/>
       <c r="N30" s="119">
         <f>SUM(N23:N29)</f>
         <v/>
@@ -3159,14 +3312,13 @@
     <row r="31" ht="12.95" customHeight="1">
       <c r="A31" s="100" t="n"/>
       <c r="B31" s="101" t="n"/>
-      <c r="C31" s="108" t="n"/>
-      <c r="D31" s="116" t="n"/>
+      <c r="C31" s="195" t="n"/>
+      <c r="D31" s="104" t="n"/>
       <c r="E31" s="104" t="n"/>
       <c r="F31" s="104" t="n"/>
       <c r="G31" s="104" t="n"/>
       <c r="H31" s="104" t="n"/>
       <c r="I31" s="104" t="n"/>
-      <c r="J31" s="105" t="n"/>
       <c r="K31" s="120" t="n"/>
       <c r="L31" s="37" t="n"/>
       <c r="M31" s="37" t="n"/>
@@ -3175,14 +3327,13 @@
     <row r="32" ht="12.95" customHeight="1">
       <c r="A32" s="121" t="n"/>
       <c r="B32" s="108" t="n"/>
-      <c r="C32" s="108" t="n"/>
-      <c r="D32" s="116" t="n"/>
+      <c r="C32" s="195" t="n"/>
+      <c r="D32" s="104" t="n"/>
       <c r="E32" s="104" t="n"/>
       <c r="F32" s="104" t="n"/>
       <c r="G32" s="104" t="n"/>
       <c r="H32" s="104" t="n"/>
       <c r="I32" s="104" t="n"/>
-      <c r="J32" s="105" t="n"/>
       <c r="K32" s="122" t="n"/>
       <c r="L32" s="123" t="inlineStr">
         <is>
@@ -3199,14 +3350,13 @@
     <row r="33" ht="12" customHeight="1">
       <c r="A33" s="121" t="n"/>
       <c r="B33" s="125" t="n"/>
-      <c r="C33" s="126" t="n"/>
-      <c r="D33" s="127" t="n"/>
+      <c r="C33" s="198" t="n"/>
+      <c r="D33" s="104" t="n"/>
       <c r="E33" s="104" t="n"/>
       <c r="F33" s="104" t="n"/>
       <c r="G33" s="104" t="n"/>
       <c r="H33" s="104" t="n"/>
       <c r="I33" s="104" t="n"/>
-      <c r="J33" s="105" t="n"/>
       <c r="K33" s="128" t="inlineStr">
         <is>
           <t>OXY</t>
@@ -3223,14 +3373,13 @@
     <row r="34" ht="11.25" customHeight="1">
       <c r="A34" s="131" t="n"/>
       <c r="B34" s="108" t="n"/>
-      <c r="C34" s="108" t="n"/>
-      <c r="D34" s="132" t="n"/>
+      <c r="C34" s="195" t="n"/>
+      <c r="D34" s="104" t="n"/>
       <c r="E34" s="104" t="n"/>
       <c r="F34" s="104" t="n"/>
       <c r="G34" s="104" t="n"/>
       <c r="H34" s="104" t="n"/>
       <c r="I34" s="104" t="n"/>
-      <c r="J34" s="105" t="n"/>
       <c r="K34" s="94" t="inlineStr">
         <is>
           <t>ACYT</t>
@@ -3247,14 +3396,13 @@
     <row r="35" ht="12.95" customHeight="1">
       <c r="A35" s="131" t="n"/>
       <c r="B35" s="108" t="n"/>
-      <c r="C35" s="108" t="n"/>
-      <c r="D35" s="132" t="n"/>
+      <c r="C35" s="195" t="n"/>
+      <c r="D35" s="104" t="n"/>
       <c r="E35" s="104" t="n"/>
       <c r="F35" s="104" t="n"/>
       <c r="G35" s="104" t="n"/>
       <c r="H35" s="104" t="n"/>
       <c r="I35" s="104" t="n"/>
-      <c r="J35" s="105" t="n"/>
       <c r="K35" s="133" t="inlineStr">
         <is>
           <t>ENGINE OIL 40wt</t>
@@ -3269,14 +3417,13 @@
     <row r="36" ht="12.95" customHeight="1">
       <c r="A36" s="131" t="n"/>
       <c r="B36" s="108" t="n"/>
-      <c r="C36" s="108" t="n"/>
-      <c r="D36" s="135" t="n"/>
+      <c r="C36" s="195" t="n"/>
+      <c r="D36" s="104" t="n"/>
       <c r="E36" s="104" t="n"/>
       <c r="F36" s="104" t="n"/>
       <c r="G36" s="104" t="n"/>
       <c r="H36" s="104" t="n"/>
       <c r="I36" s="104" t="n"/>
-      <c r="J36" s="105" t="n"/>
       <c r="K36" s="136" t="inlineStr">
         <is>
           <t xml:space="preserve">HYDRAULIC 37wt. </t>
@@ -3293,14 +3440,13 @@
     <row r="37" ht="12.95" customHeight="1">
       <c r="A37" s="100" t="n"/>
       <c r="B37" s="108" t="n"/>
-      <c r="C37" s="108" t="n"/>
-      <c r="D37" s="135" t="n"/>
+      <c r="C37" s="195" t="n"/>
+      <c r="D37" s="104" t="n"/>
       <c r="E37" s="104" t="n"/>
       <c r="F37" s="104" t="n"/>
       <c r="G37" s="104" t="n"/>
       <c r="H37" s="104" t="n"/>
       <c r="I37" s="104" t="n"/>
-      <c r="J37" s="105" t="n"/>
       <c r="K37" s="136" t="inlineStr">
         <is>
           <t>GEAR 90wt</t>
@@ -3322,14 +3468,13 @@
     <row r="38" ht="12.95" customHeight="1">
       <c r="A38" s="131" t="n"/>
       <c r="B38" s="138" t="n"/>
-      <c r="C38" s="138" t="n"/>
-      <c r="D38" s="139" t="n"/>
+      <c r="C38" s="199" t="n"/>
+      <c r="D38" s="104" t="n"/>
       <c r="E38" s="104" t="n"/>
       <c r="F38" s="104" t="n"/>
       <c r="G38" s="104" t="n"/>
       <c r="H38" s="104" t="n"/>
       <c r="I38" s="104" t="n"/>
-      <c r="J38" s="105" t="n"/>
       <c r="K38" s="136" t="inlineStr">
         <is>
           <t>A.T.F</t>
@@ -3344,14 +3489,13 @@
     <row r="39" ht="12.95" customHeight="1">
       <c r="A39" s="131" t="n"/>
       <c r="B39" s="138" t="n"/>
-      <c r="C39" s="138" t="n"/>
-      <c r="D39" s="135" t="n"/>
+      <c r="C39" s="199" t="n"/>
+      <c r="D39" s="104" t="n"/>
       <c r="E39" s="104" t="n"/>
       <c r="F39" s="104" t="n"/>
       <c r="G39" s="104" t="n"/>
       <c r="H39" s="104" t="n"/>
       <c r="I39" s="104" t="n"/>
-      <c r="J39" s="105" t="n"/>
       <c r="K39" s="136" t="inlineStr">
         <is>
           <t xml:space="preserve">GREASE    </t>
@@ -3368,7 +3512,13 @@
     <row r="40" ht="12.95" customHeight="1">
       <c r="A40" s="131" t="n"/>
       <c r="B40" s="138" t="n"/>
-      <c r="C40" s="138" t="n"/>
+      <c r="C40" s="199" t="n"/>
+      <c r="D40" s="104" t="n"/>
+      <c r="E40" s="104" t="n"/>
+      <c r="F40" s="104" t="n"/>
+      <c r="G40" s="104" t="n"/>
+      <c r="H40" s="104" t="n"/>
+      <c r="I40" s="104" t="n"/>
       <c r="K40" s="140" t="inlineStr">
         <is>
           <t>DIESEL</t>
@@ -3384,14 +3534,13 @@
     <row r="41" ht="12.95" customHeight="1">
       <c r="A41" s="131" t="n"/>
       <c r="B41" s="138" t="n"/>
-      <c r="C41" s="138" t="n"/>
-      <c r="D41" s="145" t="n"/>
+      <c r="C41" s="199" t="n"/>
+      <c r="D41" s="104" t="n"/>
       <c r="E41" s="104" t="n"/>
       <c r="F41" s="104" t="n"/>
       <c r="G41" s="104" t="n"/>
       <c r="H41" s="104" t="n"/>
       <c r="I41" s="104" t="n"/>
-      <c r="J41" s="105" t="n"/>
       <c r="K41" s="146" t="inlineStr">
         <is>
           <t>DRILLING LINE &amp; TON MILS</t>
@@ -3404,14 +3553,13 @@
     <row r="42" ht="12.95" customHeight="1">
       <c r="A42" s="131" t="n"/>
       <c r="B42" s="138" t="n"/>
-      <c r="C42" s="138" t="n"/>
-      <c r="D42" s="147" t="n"/>
+      <c r="C42" s="199" t="n"/>
+      <c r="D42" s="104" t="n"/>
       <c r="E42" s="104" t="n"/>
       <c r="F42" s="104" t="n"/>
       <c r="G42" s="104" t="n"/>
       <c r="H42" s="104" t="n"/>
       <c r="I42" s="104" t="n"/>
-      <c r="J42" s="105" t="n"/>
       <c r="K42" s="148" t="inlineStr">
         <is>
           <t>DRILLING LINE &amp; TON MILS</t>
@@ -3426,14 +3574,13 @@
     <row r="43" ht="12.95" customHeight="1">
       <c r="A43" s="131" t="n"/>
       <c r="B43" s="138" t="n"/>
-      <c r="C43" s="138" t="n"/>
-      <c r="D43" s="150" t="n"/>
+      <c r="C43" s="199" t="n"/>
+      <c r="D43" s="104" t="n"/>
       <c r="E43" s="104" t="n"/>
       <c r="F43" s="104" t="n"/>
       <c r="G43" s="104" t="n"/>
       <c r="H43" s="104" t="n"/>
       <c r="I43" s="104" t="n"/>
-      <c r="J43" s="105" t="n"/>
       <c r="K43" s="151" t="inlineStr">
         <is>
           <t xml:space="preserve">DRILLING LINE LENGTH </t>
@@ -3448,14 +3595,13 @@
     <row r="44" ht="12.95" customHeight="1">
       <c r="A44" s="131" t="n"/>
       <c r="B44" s="138" t="n"/>
-      <c r="C44" s="138" t="n"/>
-      <c r="D44" s="145" t="n"/>
+      <c r="C44" s="199" t="n"/>
+      <c r="D44" s="104" t="n"/>
       <c r="E44" s="104" t="n"/>
       <c r="F44" s="104" t="n"/>
       <c r="G44" s="104" t="n"/>
       <c r="H44" s="104" t="n"/>
       <c r="I44" s="104" t="n"/>
-      <c r="J44" s="105" t="n"/>
       <c r="K44" s="153" t="inlineStr">
         <is>
           <t>DRILLING LINE SLIP</t>
@@ -3471,14 +3617,13 @@
     <row r="45" ht="12.95" customHeight="1">
       <c r="A45" s="156" t="n"/>
       <c r="B45" s="138" t="n"/>
-      <c r="C45" s="138" t="n"/>
-      <c r="D45" s="157" t="n"/>
-      <c r="E45" s="158" t="n"/>
-      <c r="F45" s="158" t="n"/>
-      <c r="G45" s="158" t="n"/>
-      <c r="H45" s="158" t="n"/>
-      <c r="I45" s="158" t="n"/>
-      <c r="J45" s="159" t="n"/>
+      <c r="C45" s="199" t="n"/>
+      <c r="D45" s="104" t="n"/>
+      <c r="E45" s="104" t="n"/>
+      <c r="F45" s="104" t="n"/>
+      <c r="G45" s="104" t="n"/>
+      <c r="H45" s="104" t="n"/>
+      <c r="I45" s="104" t="n"/>
       <c r="K45" s="160" t="inlineStr">
         <is>
           <t>DRILLING LINE TOTAL CUT</t>
@@ -3828,17 +3973,19 @@
       <c r="M57" s="7" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="180">
+  <mergeCells count="189">
+    <mergeCell ref="C36:I36"/>
     <mergeCell ref="E3:I3"/>
     <mergeCell ref="M43:N43"/>
     <mergeCell ref="A51:B51"/>
     <mergeCell ref="J19:K19"/>
     <mergeCell ref="A49:H49"/>
     <mergeCell ref="L19:M19"/>
-    <mergeCell ref="D24:J24"/>
+    <mergeCell ref="J28:K28"/>
     <mergeCell ref="K56:M56"/>
-    <mergeCell ref="D33:J33"/>
+    <mergeCell ref="L28:M28"/>
     <mergeCell ref="B12:C12"/>
+    <mergeCell ref="C28:I28"/>
     <mergeCell ref="K35:L35"/>
     <mergeCell ref="E51:F51"/>
     <mergeCell ref="A54:B54"/>
@@ -3847,46 +3994,43 @@
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="C54:D54"/>
     <mergeCell ref="J17:M17"/>
-    <mergeCell ref="D26:J26"/>
-    <mergeCell ref="K27:M27"/>
-    <mergeCell ref="D35:J35"/>
     <mergeCell ref="C50:D50"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="F16:I16"/>
     <mergeCell ref="A1:C6"/>
+    <mergeCell ref="C30:I30"/>
     <mergeCell ref="C7:E7"/>
     <mergeCell ref="L14:M14"/>
     <mergeCell ref="A56:B56"/>
     <mergeCell ref="C56:D56"/>
     <mergeCell ref="B13:C13"/>
+    <mergeCell ref="C45:I45"/>
     <mergeCell ref="C21:G21"/>
+    <mergeCell ref="L29:M29"/>
     <mergeCell ref="K42:L42"/>
     <mergeCell ref="M36:N36"/>
     <mergeCell ref="M33:N33"/>
     <mergeCell ref="M45:N45"/>
     <mergeCell ref="I52:J52"/>
-    <mergeCell ref="K25:M25"/>
     <mergeCell ref="A53:B53"/>
+    <mergeCell ref="C31:I31"/>
     <mergeCell ref="J21:K21"/>
+    <mergeCell ref="C40:I40"/>
     <mergeCell ref="L21:M21"/>
     <mergeCell ref="K37:L37"/>
     <mergeCell ref="E53:F53"/>
+    <mergeCell ref="J23:K23"/>
     <mergeCell ref="A9:B9"/>
-    <mergeCell ref="K29:M29"/>
-    <mergeCell ref="D37:J37"/>
     <mergeCell ref="A48:B48"/>
+    <mergeCell ref="C23:I23"/>
     <mergeCell ref="G12:H12"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="E55:F55"/>
     <mergeCell ref="L16:M16"/>
-    <mergeCell ref="D39:J39"/>
     <mergeCell ref="M44:N44"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="E48:F48"/>
-    <mergeCell ref="D29:J29"/>
-    <mergeCell ref="D23:J23"/>
-    <mergeCell ref="D38:J38"/>
     <mergeCell ref="C20:G20"/>
     <mergeCell ref="C47:D47"/>
     <mergeCell ref="I54:J54"/>
@@ -3894,6 +4038,9 @@
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="I7:J7"/>
     <mergeCell ref="A46:B46"/>
+    <mergeCell ref="C34:I34"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="C42:I42"/>
     <mergeCell ref="K7:M7"/>
     <mergeCell ref="F17:G17"/>
     <mergeCell ref="I56:J56"/>
@@ -3904,58 +4051,67 @@
     <mergeCell ref="J20:K20"/>
     <mergeCell ref="K43:L43"/>
     <mergeCell ref="L20:M20"/>
+    <mergeCell ref="C29:I29"/>
     <mergeCell ref="A8:B8"/>
-    <mergeCell ref="D27:J27"/>
+    <mergeCell ref="K41:N41"/>
     <mergeCell ref="F9:G9"/>
-    <mergeCell ref="K41:N41"/>
+    <mergeCell ref="C44:I44"/>
+    <mergeCell ref="C22:I22"/>
     <mergeCell ref="J12:K12"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="A52:B52"/>
     <mergeCell ref="C53:D53"/>
     <mergeCell ref="J48:K48"/>
     <mergeCell ref="L48:M48"/>
-    <mergeCell ref="D28:J28"/>
     <mergeCell ref="E50:F50"/>
+    <mergeCell ref="J22:M22"/>
+    <mergeCell ref="J29:K29"/>
     <mergeCell ref="M34:N34"/>
     <mergeCell ref="G11:H11"/>
-    <mergeCell ref="D25:J25"/>
     <mergeCell ref="C9:E9"/>
     <mergeCell ref="I49:M49"/>
-    <mergeCell ref="D30:J30"/>
+    <mergeCell ref="E52:F52"/>
     <mergeCell ref="K45:L45"/>
-    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="C32:I32"/>
     <mergeCell ref="M39:N39"/>
+    <mergeCell ref="C38:I38"/>
     <mergeCell ref="L47:M47"/>
     <mergeCell ref="E46:M46"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="L24:M24"/>
     <mergeCell ref="D4:G5"/>
     <mergeCell ref="L18:M18"/>
     <mergeCell ref="K44:L44"/>
+    <mergeCell ref="C24:I24"/>
     <mergeCell ref="G13:H13"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="L8:M8"/>
+    <mergeCell ref="C33:I33"/>
     <mergeCell ref="F10:I10"/>
     <mergeCell ref="M40:N40"/>
     <mergeCell ref="A55:B55"/>
     <mergeCell ref="F8:G8"/>
-    <mergeCell ref="D31:J31"/>
+    <mergeCell ref="J26:K26"/>
     <mergeCell ref="G47:I47"/>
+    <mergeCell ref="L26:M26"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="C46:D46"/>
+    <mergeCell ref="C26:I26"/>
     <mergeCell ref="G15:H15"/>
     <mergeCell ref="J16:K16"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="M37:N37"/>
     <mergeCell ref="C51:D51"/>
     <mergeCell ref="H8:J8"/>
-    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="C35:I35"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="L25:M25"/>
     <mergeCell ref="C48:D48"/>
+    <mergeCell ref="C25:I25"/>
     <mergeCell ref="L9:M9"/>
     <mergeCell ref="K31:N31"/>
-    <mergeCell ref="D32:J32"/>
-    <mergeCell ref="K24:M24"/>
     <mergeCell ref="G51:H51"/>
     <mergeCell ref="I51:J51"/>
-    <mergeCell ref="D41:J41"/>
     <mergeCell ref="E54:F54"/>
     <mergeCell ref="G54:H54"/>
     <mergeCell ref="M38:N38"/>
@@ -3963,51 +4119,49 @@
     <mergeCell ref="G50:H50"/>
     <mergeCell ref="H9:J9"/>
     <mergeCell ref="I50:J50"/>
-    <mergeCell ref="K26:M26"/>
     <mergeCell ref="K51:M51"/>
-    <mergeCell ref="D43:J43"/>
     <mergeCell ref="E56:F56"/>
     <mergeCell ref="G56:H56"/>
     <mergeCell ref="K50:M50"/>
     <mergeCell ref="G52:H52"/>
+    <mergeCell ref="C39:I39"/>
     <mergeCell ref="J14:K14"/>
-    <mergeCell ref="D42:J42"/>
     <mergeCell ref="J13:K13"/>
     <mergeCell ref="K36:L36"/>
     <mergeCell ref="K52:M52"/>
     <mergeCell ref="L13:M13"/>
-    <mergeCell ref="D44:J44"/>
+    <mergeCell ref="C37:I37"/>
+    <mergeCell ref="J30:K30"/>
     <mergeCell ref="J15:K15"/>
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="L15:M15"/>
     <mergeCell ref="C55:D55"/>
-    <mergeCell ref="D34:J34"/>
     <mergeCell ref="G53:H53"/>
     <mergeCell ref="I53:J53"/>
+    <mergeCell ref="L23:M23"/>
     <mergeCell ref="K53:M53"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="A10:C10"/>
-    <mergeCell ref="D22:J22"/>
-    <mergeCell ref="D36:J36"/>
-    <mergeCell ref="K28:M28"/>
     <mergeCell ref="I55:J55"/>
-    <mergeCell ref="D45:J45"/>
     <mergeCell ref="A47:B47"/>
     <mergeCell ref="M42:N42"/>
     <mergeCell ref="G14:H14"/>
     <mergeCell ref="C52:D52"/>
     <mergeCell ref="K39:L39"/>
     <mergeCell ref="J47:K47"/>
+    <mergeCell ref="C41:I41"/>
     <mergeCell ref="G55:H55"/>
     <mergeCell ref="A20:B20"/>
-    <mergeCell ref="K22:N22"/>
     <mergeCell ref="K38:L38"/>
     <mergeCell ref="M32:N32"/>
     <mergeCell ref="K54:M54"/>
+    <mergeCell ref="C43:I43"/>
     <mergeCell ref="J18:K18"/>
     <mergeCell ref="K55:M55"/>
     <mergeCell ref="G48:I48"/>
+    <mergeCell ref="L27:M27"/>
     <mergeCell ref="D1:J2"/>
+    <mergeCell ref="C27:I27"/>
     <mergeCell ref="E47:F47"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
